--- a/data/06_genomic_function/functional_notes.xlsx
+++ b/data/06_genomic_function/functional_notes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -394,7 +394,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Similar to Aifm1: Apoptosis-inducing factor 1%2C mitochondrial (Mus musculus)</t>
+          <t>Similar to ADAMTS7: A disintegrin and metalloproteinase with thrombospondin motifs 7 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C3">
@@ -409,7 +409,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Similar to CNNM4: Metal transporter CNNM4 (Homo sapiens)</t>
+          <t>Similar to AHI1: Jouberin (Homo sapiens)</t>
         </is>
       </c>
       <c r="C4">
@@ -424,7 +424,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Similar to Cd81: CD81 antigen (Rattus norvegicus)</t>
+          <t>Similar to LRP1: Low-density lipoprotein receptor-related protein 1 (Gallus gallus)</t>
         </is>
       </c>
       <c r="C5">
@@ -439,7 +439,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Similar to Ctnnd1: Catenin delta-1 (Mus musculus)</t>
+          <t>Similar to MAST1: Microtubule-associated serine/threonine-protein kinase 1 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C6">
@@ -454,7 +454,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Similar to DHRS4: Dehydrogenase/reductase SDR family member 4 (Sus scrofa)</t>
+          <t>Similar to MRC1: Macrophage mannose receptor 1 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C7">
@@ -469,7 +469,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Similar to DHX9: ATP-dependent RNA helicase A (Bos taurus)</t>
+          <t>Similar to SFRP2: Secreted frizzled-related protein 2 (Canis lupus familiaris)</t>
         </is>
       </c>
       <c r="C8">
@@ -484,7 +484,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Similar to Dync1h1: Cytoplasmic dynein 1 heavy chain 1 (Rattus norvegicus)</t>
+          <t>Similar to WBP2NL: Postacrosomal sheath WW domain-binding protein (Homo sapiens)</t>
         </is>
       </c>
       <c r="C9">
@@ -499,7 +499,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Similar to ERCC6: DNA excision repair protein ERCC-6 (Homo sapiens)</t>
+          <t>Similar to cpeb1: Cytoplasmic polyadenylation element-binding protein 1 (Carassius auratus)</t>
         </is>
       </c>
       <c r="C10">
@@ -514,7 +514,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Similar to EXOC2: Exocyst complex component 2 (Homo sapiens)</t>
+          <t>Similar to dlc: Delta-like protein C (Danio rerio)</t>
         </is>
       </c>
       <c r="C11">
@@ -529,7 +529,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Similar to Eftud2: 116 kDa U5 small nuclear ribonucleoprotein component (Mus musculus)</t>
+          <t>Similar to pol: Retrovirus-related Pol polyprotein from transposon 17.6 (Drosophila melanogaster)</t>
         </is>
       </c>
       <c r="C12">
@@ -544,7 +544,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Similar to GALNT8: Probable polypeptide N-acetylgalactosaminyltransferase 8 (Homo sapiens)</t>
+          <t>Similar to slc25a26: S-adenosylmethionine mitochondrial carrier protein (Danio rerio)</t>
         </is>
       </c>
       <c r="C13">
@@ -559,7 +559,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Similar to Grm8: Metabotropic glutamate receptor 8 (Rattus norvegicus)</t>
+          <t>Similar to zgc:113413: Natterin-like protein (Danio rerio)</t>
         </is>
       </c>
       <c r="C14">
@@ -572,54 +572,49 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Similar to KANSL1: KAT8 regulatory NSL complex subunit 1 (Homo sapiens)</t>
-        </is>
-      </c>
       <c r="C15">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Similar to MR1: Major histocompatibility complex class I-related gene protein (Bos taurus)</t>
+          <t>Protein of unknown function</t>
         </is>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Similar to Mtor: Serine/threonine-protein kinase mTOR (Rattus norvegicus)</t>
+          <t>Similar to ARID2: AT-rich interactive domain-containing protein 2 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Similar to Nsd1: Histone-lysine N-methyltransferase%2C H3 lysine-36 and H4 lysine-20 specific (Mus musculus)</t>
+          <t>Similar to ASAP3: Arf-GAP with SH3 domain%2C ANK repeat and PH domain-containing protein 3 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C18">
@@ -629,12 +624,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Similar to Plec: Plectin (Mus musculus)</t>
+          <t>Similar to ATP13A3: Probable cation-transporting ATPase 13A3 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C19">
@@ -644,12 +639,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Similar to Pnpla8: Calcium-independent phospholipase A2-gamma (Mus musculus)</t>
+          <t>Similar to Arhgap17: Rho GTPase-activating protein 17 (Rattus norvegicus)</t>
         </is>
       </c>
       <c r="C20">
@@ -659,12 +654,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Similar to Prkcd: Protein kinase C delta type (Mus musculus)</t>
+          <t>Similar to C19orf43: Uncharacterized protein C19orf43 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C21">
@@ -674,12 +669,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Similar to QRICH2: Glutamine-rich protein 2 (Homo sapiens)</t>
+          <t>Similar to CASP10: Caspase-10 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C22">
@@ -689,12 +684,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Similar to RASSF5: Ras association domain-containing protein 5 (Homo sapiens)</t>
+          <t>Similar to DHRS4: Dehydrogenase/reductase SDR family member 4 (Sus scrofa)</t>
         </is>
       </c>
       <c r="C23">
@@ -704,12 +699,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Similar to RFX1: MHC class II regulatory factor RFX1 (Homo sapiens)</t>
+          <t>Similar to DUSP6: Dual specificity protein phosphatase 6 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C24">
@@ -719,12 +714,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Similar to SEMA6D: Semaphorin-6D (Pongo abelii)</t>
+          <t>Similar to Dph3: DPH3 homolog (Mus musculus)</t>
         </is>
       </c>
       <c r="C25">
@@ -734,12 +729,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Similar to SF1: Splicing factor 1 (Homo sapiens)</t>
+          <t>Similar to Elavl4: ELAV-like protein 4 (Mus musculus)</t>
         </is>
       </c>
       <c r="C26">
@@ -749,12 +744,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Similar to SKIL: Ski-like protein (Pongo abelii)</t>
+          <t>Similar to Ephb2: Ephrin type-B receptor 2 (Mus musculus)</t>
         </is>
       </c>
       <c r="C27">
@@ -764,12 +759,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Similar to Slc26a5: Prestin (Rattus norvegicus)</t>
+          <t>Similar to FAM63B: Protein FAM63B (Homo sapiens)</t>
         </is>
       </c>
       <c r="C28">
@@ -779,12 +774,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Similar to TACR1: Substance-P receptor (Lithobates catesbeiana)</t>
+          <t>Similar to FOXJ3: Forkhead box protein J3 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C29">
@@ -794,12 +789,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Similar to TNRC6C: Trinucleotide repeat-containing gene 6C protein (Homo sapiens)</t>
+          <t>Similar to Fam169b: Protein FAM169B (Mus musculus)</t>
         </is>
       </c>
       <c r="C30">
@@ -809,12 +804,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Similar to TXNRD3: Thioredoxin reductase 3 (Homo sapiens)</t>
+          <t>Similar to GSE1: Genetic suppressor element 1 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C31">
@@ -824,12 +819,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Similar to UBR7: Putative E3 ubiquitin-protein ligase UBR7 (Homo sapiens)</t>
+          <t>Similar to HK1: Hexokinase-1 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C32">
@@ -839,12 +834,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Similar to acta1: Actin%2C alpha skeletal muscle (Oryzias latipes)</t>
+          <t>Similar to KLHL12: Kelch-like protein 12 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C33">
@@ -854,12 +849,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Similar to chtf18: Chromosome transmission fidelity protein 18 homolog (Xenopus laevis)</t>
+          <t>Similar to MARS: Methionine--tRNA ligase%2C cytoplasmic (Homo sapiens)</t>
         </is>
       </c>
       <c r="C34">
@@ -869,12 +864,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Similar to fzd1: Frizzled-1 (Xenopus laevis)</t>
+          <t>Similar to METTL24: Methyltransferase-like protein 24 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C35">
@@ -884,12 +879,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Similar to med29: Mediator of RNA polymerase II transcription subunit 29 (Danio rerio)</t>
+          <t>Similar to MR1: Major histocompatibility complex class I-related gene protein (Pongo abelii)</t>
         </is>
       </c>
       <c r="C36">
@@ -899,12 +894,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Similar to plpp7: Inactive phospholipid phosphatase 7 (Danio rerio)</t>
+          <t>Similar to PAPD7: Non-canonical poly(A) RNA polymerase PAPD7 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C37">
@@ -914,11 +909,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Similar to PDX1: Pancreas/duodenum homeobox protein 1 (Pan troglodytes)</t>
         </is>
       </c>
       <c r="C38">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -929,11 +929,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Protein of unknown function</t>
+          <t>Similar to Ppp1r9b: Neurabin-2 (Rattus norvegicus)</t>
         </is>
       </c>
       <c r="C39">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -944,7 +944,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Similar to ALK: ALK tyrosine kinase receptor (Homo sapiens)</t>
+          <t>Similar to QRICH1: Glutamine-rich protein 1 (Bos taurus)</t>
         </is>
       </c>
       <c r="C40">
@@ -959,7 +959,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Similar to Bach1: Transcription regulator protein BACH1 (Mus musculus)</t>
+          <t>Similar to RAB33B: Ras-related protein Rab-33B (Pongo abelii)</t>
         </is>
       </c>
       <c r="C41">
@@ -974,7 +974,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Similar to Dgkb: Diacylglycerol kinase beta (Mus musculus)</t>
+          <t>Similar to Rasl10b: Ras-like protein family member 10B (Mus musculus)</t>
         </is>
       </c>
       <c r="C42">
@@ -989,7 +989,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Similar to FBLN2: Fibulin-2 (Homo sapiens)</t>
+          <t>Similar to SARS2: Serine--tRNA ligase%2C mitochondrial (Bos taurus)</t>
         </is>
       </c>
       <c r="C43">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Similar to GUCA1A: Guanylyl cyclase-activating protein 1 (Gallus gallus)</t>
+          <t>Similar to SEMA6D: Semaphorin-6D (Pongo abelii)</t>
         </is>
       </c>
       <c r="C44">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Similar to LTBP3: Latent-transforming growth factor beta-binding protein 3 (Homo sapiens)</t>
+          <t>Similar to SLC16A5: Monocarboxylate transporter 6 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C45">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Similar to MAST1: Microtubule-associated serine/threonine-protein kinase 1 (Homo sapiens)</t>
+          <t>Similar to SNX33: Sorting nexin-33 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C46">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Similar to MSI1: RNA-binding protein Musashi homolog 1 (Homo sapiens)</t>
+          <t>Similar to SORL1: Sortilin-related receptor (Oryctolagus cuniculus)</t>
         </is>
       </c>
       <c r="C47">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Similar to SEMA7A: Semaphorin-7A (Homo sapiens)</t>
+          <t>Similar to Slc30a4: Zinc transporter 4 (Rattus norvegicus)</t>
         </is>
       </c>
       <c r="C48">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Similar to TNFAIP6: Tumor necrosis factor-inducible gene 6 protein (Homo sapiens)</t>
+          <t>Similar to TET2: Methylcytosine dioxygenase TET2 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C49">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Similar to Tlr8: Toll-like receptor 8 (Mus musculus)</t>
+          <t>Similar to TMEM119: Transmembrane protein 119 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C50">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Similar to Ttn: Titin (Mus musculus)</t>
+          <t>Similar to TMEM260: Transmembrane protein 260 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C51">
@@ -1124,11 +1124,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Similar to USP18: Ubl carboxyl-terminal hydrolase 18 (Homo sapiens)</t>
+          <t>Similar to TRIM16: Tripartite motif-containing protein 16 (Homo sapiens)</t>
         </is>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Similar to luzp2: Leucine zipper protein 2 (Danio rerio)</t>
+          <t>Similar to TRMT1: tRNA (guanine(26)-N(2))-dimethyltransferase (Homo sapiens)</t>
         </is>
       </c>
       <c r="C53">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Similar to tgl2: Protein-glutamine gamma-glutamyltransferase 2 (Pagrus major)</t>
+          <t>Similar to Tbc1d17: TBC1 domain family member 17 (Mus musculus)</t>
         </is>
       </c>
       <c r="C54">
@@ -1167,7 +1167,127 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Similar to jag1b: Protein jagged-1b (Danio rerio)</t>
+        </is>
+      </c>
       <c r="C55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Similar to kdelr2: ER lumen protein-retaining receptor 2 (Danio rerio)</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Similar to klhl21: Kelch-like protein 21 (Danio rerio)</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Similar to plpp7: Inactive phospholipid phosphatase 7 (Danio rerio)</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Similar to pola1: DNA polymerase alpha catalytic subunit (Xenopus laevis)</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Similar to zgc:153454: Mediator of RNA polymerase II transcription subunit 13-like (Danio rerio)</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Similar to znf503: Zinc finger protein 503 (Danio rerio)</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Similar to znrf1: E3 ubiquitin-protein ligase znrf1 (Danio rerio)</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C63">
         <v>13</v>
       </c>
     </row>
